--- a/assets/constructions/examples/ctd_mb1.xlsx
+++ b/assets/constructions/examples/ctd_mb1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL6"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,51 +619,80 @@
           <t>cpdf</t>
         </is>
       </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ФК 4067-3-8-52-4-Z2 Р18 1615</t>
+          <t>113RXT-d2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ТИЗ</t>
+          <t>ILIX</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ФК 4067</t>
+          <t>113RXT-TALICARB</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PNKS</t>
+          <t>PMKNSO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>H</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>h10</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>HA-4</t>
+          <t>HB-6</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -673,46 +702,44 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Р18</t>
-        </is>
-      </c>
+      <c r="S2" t="inlineStr"/>
       <c r="T2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>XTreme</t>
         </is>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Нормаль завода</t>
+          <t>DIN 6527 L</t>
         </is>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="AA2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>30</v>
+      </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
@@ -723,12 +750,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2019 / ТИЗ Каталог высокоточных инструментов</t>
+          <t>2007/Монолитный ТС инструмент.pdf</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>HSS</t>
+          <t>VHM</t>
         </is>
       </c>
       <c r="AK2" t="b">
@@ -736,52 +763,67 @@
       </c>
       <c r="AL2" t="b">
         <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>PMKNSHO</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C21.160B080.WT</t>
+          <t>MC416-20.0W4L-WJ30TF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BRICE</t>
+          <t>WALTER</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C21-B-T</t>
+          <t>MC416</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PMK</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>MKNS</t>
+        </is>
+      </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>e8</t>
+          <t>h7</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>HB-16</t>
+          <t>HA-20</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -791,23 +833,27 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>HA</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Q3" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
           <t>h6</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>WJ30TF</t>
+        </is>
+      </c>
       <c r="T3" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr">
@@ -815,18 +861,20 @@
           <t>TiAlN</t>
         </is>
       </c>
-      <c r="W3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>PWZ-NORM L</t>
+        </is>
+      </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="AA3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AB3" t="n">
         <v>30</v>
@@ -834,7 +882,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
@@ -843,7 +891,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Спецпозиция</t>
+          <t>2017/Общий каталог WALTER 2017</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -855,53 +903,68 @@
         <v>0</v>
       </c>
       <c r="AL3" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>PMKNS</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>40101200T075 TIALN</t>
+          <t>213RTC-d9.5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>ILIX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>213RTC-TALICARB</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PMK</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+          <t>PMKNSO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>e8</t>
+          <t>h10</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>4.75</v>
       </c>
       <c r="K4" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>HA-12</t>
+          <t>HA-10</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -915,40 +978,36 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="Q4" t="n">
-        <v>75</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>h6</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>TIALN</t>
-        </is>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="n">
-        <v>75</v>
+        <v>19</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>TiCN</t>
         </is>
       </c>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>DIN 6527 L</t>
+        </is>
+      </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="AA4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AB4" t="n">
         <v>30</v>
@@ -963,7 +1022,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2020/End Mills Widia Hanita RU</t>
+          <t>2007/Монолитный ТС инструмент.pdf</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -976,56 +1035,67 @@
       </c>
       <c r="AL4" t="b">
         <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>PMKNSHO</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>715006002RT TIALN-RT1</t>
+          <t>GMG56250</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>YG1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>GMG56</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>SH</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>e8</t>
+          <t>0/-0,03</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>12.5</v>
       </c>
       <c r="K5" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
         <v>4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HB-25</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1035,14 +1105,14 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1051,31 +1121,35 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>TIALN-RT1</t>
+          <t>MGHM</t>
         </is>
       </c>
       <c r="T5" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>TiAlN</t>
+          <t>AlTiN</t>
         </is>
       </c>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>YG STD</t>
+        </is>
+      </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="AA5" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="AB5" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
@@ -1087,7 +1161,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>2020/End Mills Widia Hanita RU</t>
+          <t>2017 - YG1 - Фрезы цельные</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1100,52 +1174,75 @@
       </c>
       <c r="AL5" t="b">
         <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>684.89</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AP5" t="n">
+        <v>62964.47</v>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>PKSH</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HMS210D03ST</t>
+          <t>7N0100302RJ TIALN-RJ1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FRESAL</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HMS210ST</t>
+          <t>7N01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PMK</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0.3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>h10</t>
+          <t>e8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>1.5</v>
+        <v>0.15</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>HA-3</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1159,10 +1256,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>0.3</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1171,32 +1268,32 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>HM HARD METALL</t>
+          <t>TIALN-RJ1</t>
         </is>
       </c>
       <c r="T6" t="n">
-        <v>8</v>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>HM HARD METALL</t>
-        </is>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr">
         <is>
-          <t>TiSiN</t>
+          <t>TiAlN</t>
         </is>
       </c>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>JIS</t>
+        </is>
+      </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AA6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AB6" t="n">
         <v>30</v>
@@ -1211,7 +1308,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2020/FRESAL Фрезы Цельные Твердосплавные</t>
+          <t>2020/End Mills Widia Hanita RU</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1224,6 +1321,17 @@
       </c>
       <c r="AL6" t="b">
         <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>PH</t>
+        </is>
       </c>
     </row>
   </sheetData>
